--- a/竞品健康险产品数据/insurance-kb/保险产品对比总表.xlsx
+++ b/竞品健康险产品数据/insurance-kb/保险产品对比总表.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y12"/>
+  <dimension ref="A1:Y13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -719,7 +719,7 @@
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>https://life.pingan.com/ilife-home/product/getPlanClausePdf?planCode=1804&amp;versionNo=1804-1&amp;attachmentType=7; https://life.pingan.com/ilife-home/product/getPlanClausePdf?planCode=1804&amp;versionNo=1804-1&amp;attachmentType=2; https://life.pingan.com/gongkaixinxipilu/baoxianchanpinmulujitiaokuan.jsp</t>
+          <t>https://life.pingan.com/ilife-home/product/getPlanClausePdf?planCode=1804&amp;versionNo=1804-1&amp;attachmentType=7; https://life.pingan.com/ilife-home/product/getPlanClausePdf?planCode=1804&amp;versionNo=1804-1&amp;attachmentType=2; https://life.pingan.com/gongkaixinxipilu/baoxianchanpinmulujitiaokuan.jsp; https://news.vobao.com/article/1180861908526700497.shtml</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>https://www.cpic.com.cn/xrsbx/gkxxpl/hlwbxxx/hlwbxcpxx/; https://www.shenlanbao.com/pingce/1465298109241958400; https://www.xiaoyusan.com/insurance/detail?id=178994</t>
+          <t>https://www.cpic.com.cn/xrsbx/gkxxpl/hlwbxxx/hlwbxcpxx/; https://www.shenlanbao.com/pingce/1465298109241958400; https://www.xiaoyusan.com/insurance/detail?id=178994; https://www.shenlanbao.com/zhinan/2097246707183636480</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>https://m.taikanglife.com/publicinfonew/specialinfo/esalesinfonew/productinfonew/list_494_1.html; https://news.vobao.com/article/1161602721810210230.shtml; https://www.naibabao.com/ketang/54491.html</t>
+          <t>https://m.taikanglife.com/publicinfonew/specialinfo/esalesinfonew/productinfonew/list_494_1.html; https://news.vobao.com/article/1161602721810210230.shtml; https://www.naibabao.com/ketang/54491.html; https://www.taikanglife.com/publicinfonew/specialinfo/esalesinfonew/productinfonew/list_494_1.html</t>
         </is>
       </c>
     </row>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>https://news.vobao.com/article/1150974914618284736.shtml; https://m.vobao.com/p/zhongguorenbao/1151070214070145540.shtml; https://e.picc.com.cn/allproduct/</t>
+          <t>https://news.vobao.com/article/1150974914618284736.shtml; https://m.vobao.com/p/zhongguorenbao/1151070214070145540.shtml; https://e.picc.com.cn/allproduct/; https://news.vobao.com/ceping/2/list_2.shtml</t>
         </is>
       </c>
     </row>
@@ -1570,7 +1570,7 @@
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>https://news.vobao.com/article/1150110253536972609.shtml; https://life.cntaiping.com/info-zstscp/; https://news.vobao.com/article/1179394292426545459.shtml</t>
+          <t>https://news.vobao.com/article/1150110253536972609.shtml; https://life.cntaiping.com/info-zstscp/; https://news.vobao.com/article/1179394292426545459.shtml; https://life.cntaiping.com/info-zstscp/?source=sy</t>
         </is>
       </c>
     </row>
@@ -1693,7 +1693,7 @@
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>https://www.shenlanbao.com/pingce/1410351806239555584; https://zhuanlan.zhihu.com/p/2071185799752725980; https://www.shenlanbao.com/zhinan/2027268745348902912</t>
+          <t>https://www.shenlanbao.com/pingce/1410351806239555584; https://zhuanlan.zhihu.com/p/2071185799752725980; https://www.shenlanbao.com/zhinan/2027268745348902912; https://news.vobao.com/article/1181410347309926609.shtml; https://m.huize.com/special/detail-29035.html</t>
         </is>
       </c>
     </row>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>https://www.xiaoyusan.com/shk/wkpage/article/index.html?articleid=300011585; https://www.shenlanbao.com/zhinan/2027268745348902912; https://zhuanlan.zhihu.com/p/2040757604692006407; https://www.naibabao.com/wenda/28318.html; https://www.xiaoyusan.com/insurance/detail?chn=h5index&amp;subchn=new_user&amp;id=179542; https://m.huize.com/study/detail-573133.html; https://www.163.com/dy/article/KR73UGO8055659JN.html</t>
+          <t>https://www.xiaoyusan.com/shk/wkpage/article/index.html?articleid=300011585; https://www.shenlanbao.com/zhinan/2027268745348902912; https://zhuanlan.zhihu.com/p/2040757604692006407; https://www.naibabao.com/wenda/28318.html; https://www.xiaoyusan.com/insurance/detail?chn=h5index&amp;subchn=new_user&amp;id=179542; https://m.huize.com/study/detail-573133.html; https://www.163.com/dy/article/KR73UGO8055659JN.html; https://www.shenlanbao.com/zhinan/2097246707183636480; https://www.xiaoyusan.com/shk/wkpage/bxzs/300013308?type=11; https://m.huize.com/special/detail-29035.html</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15日（慧择官方定制专题站问答原文：自签收守卫者7号重疾险合同或收到电子保单之日起（二者较早之日），有15日的犹豫期，犹豫期内退保没有损失；2026-09-13填充）</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1939,7 +1939,130 @@
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>https://www.shenlanbao.com/pingce/1318168497491734528; https://shouweizhe.huize.com/; https://news.vobao.com/article/1126005380168366511.shtml</t>
+          <t>https://www.shenlanbao.com/pingce/1318168497491734528; https://shouweizhe.huize.com/; https://news.vobao.com/article/1126005380168366511.shtml; https://shouweizhe7.huize.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>CI-12</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>超级玛丽17号重大疾病保险（承保方由君龙人寿变更为海保人寿；备案名未披露）</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>海保人寿保险股份有限公司</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>互联网（慧择/小雨伞/深蓝保等平台销售）</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>出生满30天至50周岁</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>保终身（当前在售）；保至70周岁版本官方称后续上线（尚未上线）</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>180天（等待期内非因意外出险不承担赔付责任；等待期内确诊中轻症则该种疾病责任终止、其他责任继续——慧择问答口径）</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>单次赔付，消费型为主（可选身故/重疾多次赔等；基础责任自带被保人豁免、结节关爱金与癌症拓展金）</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>最高基本保额50万（慧择/小雨伞口径）；起投保额未披露</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>10年/15年/20年/30年/35年交</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>110种重大疾病（其中28种为行业统一规范定义，口径承系列前代）／赔付1次100%基本保额；重疾赔付后非同组轻中症继续有效、无间隔期；可选疾病关爱金：45岁前重疾额外赔100%、45-60岁额外赔80%（限1次）；可选重疾多次赔：65岁前首次重疾后第2、3次各额外赔120%保额（不同种间隔1年、同种间隔2年，不赔同种持续状态，保留系列同种重疾可再赔优势）</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>35种中症／每次60%基本保额／与轻症合计最多6次；重疾赔付后非同组中症继续赔；可选疾病关爱金：60岁前首次中症额外赔50%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>40种轻症／每次30%基本保额／与中症合计最多6次；重疾赔付后非同组轻症继续赔</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>①三大结节关爱金（基础责任）：肺/乳腺/甲状腺良性结节切除术后满365天确诊对应部位重度癌症，分别额外赔30%/15%/15%基本保额，各自限赔1次（16号为乳腺/甲状腺仅赔其一，17号升级为各自可赔）；②癌症拓展保险金（基础责任）：首次确诊原位癌或轻度癌症后再确诊恶性肿瘤——重度，额外赔50%基本保额；③可选癌前病变手术关爱金（本代新增）：6种癌前病变手术（肺结节切除术、萎缩性胃炎伴肠上皮化生、Barrett食管、多发性大肠腺瘤性息肉、乳腺导管上皮非典型增生IIIa/IIIb级、宫颈上皮内瘤变CIN III）每次赔5%基本保额、每种限1次、累计上限30%（30岁男50万保额附加费约140元/年，深蓝保）；④可选恶性肿瘤——重度医疗津贴：首次重疾后再确诊癌症累计赔3次、依次40%/50%/30%保额（非癌→癌间隔180天；癌→癌的新发/复发/转移/持续均仅隔1年）；⑤可选癌症特药保险金：确诊重度癌症并接受特定治疗/使用癌症特药，额外赔50%基本保额，限1次</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>可选身故或全残保险金（不选则为消费型纯重疾）；具体给付规则（18岁前后差异等）各测评文未完整披露，以条款为准</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>被保人豁免为必选责任：确诊轻症/中症/重疾即豁免后续未交保费、保障继续（15号/16号时期为可选附加，17号纳入必选）；另有可选投保人豁免（投保人确诊重疾/中症/轻症或身故全残）</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="n">
+        <v>6720</v>
+      </c>
+      <c r="V13" s="2" t="n">
+        <v>6285</v>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>超级玛丽17号·30岁·50万保额·30年交·保终身·仅基础（必选）责任：男6720元/年、女6285元/年（小雨伞上线测评）；同口径30万保额：男4032元/年、女3771元/年（小雨伞/慧择一致）；30万保额附加癌前病变手术关爱金：男4116元/年、女3951元/年（小雨伞）。注：深蓝保称其基础价与达尔文12号基本打平；『较前序优惠20%-30%』系平台宣传口径（见highlights待注）</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>本代核心变化：承保方由君龙人寿变更为海保人寿；取消16号Pro标志性的重疾医疗保险金（『先赔再报』），改为新增癌前病变手术关爱金（保障前置到癌前阶段）；轻中症豁免改必选；结节关爱金升级为三项各自可赔。定价：深蓝保称基础价与顶流达尔文系列基本打平（50万30年交30岁男6720/女6285 vs 达尔文12号6710/6290，口径吻合）；但小鱼伞『较前序版本优惠20%-30%』与奶爸保16号Pro基础价（男6300/女6150）直接对比并不更低，疑为不同责任组合口径，留存待核。短板：等待期180天；身故责任给付细节未完整披露；保至70岁版本未上线，定期需求暂无法满足。</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.shenlanbao.com/zhinan/2097246707183636480; https://www.xiaoyusan.com/shk/wkpage/bxzs/300013308?type=11; https://m.huize.com/study/detail-577963.html</t>
         </is>
       </c>
     </row>
@@ -2664,10 +2787,12 @@
           <t>就医绿通、费用垫付类服务（以投保页为准）；家庭投保折扣：立减5%、3人立减10%</t>
         </is>
       </c>
-      <c r="U6" s="2" t="inlineStr"/>
+      <c r="U6" s="2" t="n">
+        <v>280</v>
+      </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>30岁，有社保，首年保费（第三方软文口径"约300多元/年"，非官方费率表数字）</t>
+          <t>30岁，有社保，首次投保基准年保费。按官网产品页基础责任组合加总：住院费用医疗保险2025版E款必选责任（一般医疗300万+重疾特疾600万+外购药械+质子重离子600万）190元+恶性肿瘤院外特种药品费用保险金19元+临床急需进口药品及进口器械28元+恶性肿瘤海外医疗13元+附加扩展门（急）诊医疗保险B款（保额1万）30元=280元/年；未计投保立减5%/2人立减5%/3人以上9折，不含可选津贴、疾病/意外门急诊等可选责任</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -2677,7 +2802,7 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>https://www.tk.cn/newpc/productCenter/detail/S2025102301; https://cj.sina.cn/articles/view/1813776593/6c1c08d1001013ruk; https://www.163.com/dy/article/KVG7UGP00556JONV.html; https://news.vobao.com/article/1172421314392564084.shtml; https://m.shenlanbao.com/wenda/12-471215</t>
+          <t>https://www.tk.cn/newpc/productCenter/detail/S2025102301; https://cj.sina.cn/articles/view/1813776593/6c1c08d1001013ruk; https://www.163.com/dy/article/KVG7UGP00556JONV.html; https://news.vobao.com/article/1172421314392564084.shtml; https://m.shenlanbao.com/wenda/12-471215; https://www.tk.cn/cms-zx/20250411/aeb7ad01942144ba8265f890e11c13e1.pdf; https://www.tk.cn/cms-zx/historypublic/historypublic/878a627a67c943f4a86c.pdf; https://www.tk.cn/cms-zx/productFactory/product/ZH10N0505/3/泰康在线·泰爱保·百万医疗2026说明书.pdf; https://www.tk.cn/cms-zx/20260828/6b4471e003ad4bc1986a112788374e8b.pdf; https://www.tk.cn/zxpublicinfo2023/</t>
         </is>
       </c>
     </row>
@@ -3272,7 +3397,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W8"/>
+  <dimension ref="A1:W9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3531,7 +3656,7 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>https://xuexi.huize.com/special/detail-31241.html; https://www.kaixinbao.com/zixun/358639.shtml; https://www.shenlanbao.com/zhinan/2090281043176710144; https://www.xiaoyusan.com/insurance/detail?id=179073</t>
+          <t>https://xuexi.huize.com/special/detail-31241.html; https://www.kaixinbao.com/zixun/358639.shtml; https://www.shenlanbao.com/zhinan/2090281043176710144; https://www.xiaoyusan.com/insurance/detail?id=179073; https://xuexi.huize.com/special/detail-31895.html; https://xuexi.huize.com/special/detail-31767.html</t>
         </is>
       </c>
     </row>
@@ -3650,7 +3775,7 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>https://www.shenlanbao.com/pingce/1422531538876235776; https://www.pulanbx.com/bxzs/231631.html; https://m.huize.com/study/detail-504661.html; https://www.huize.com/product/detail-104305.html</t>
+          <t>https://www.shenlanbao.com/pingce/1422531538876235776; https://www.pulanbx.com/bxzs/231631.html; https://m.huize.com/study/detail-504661.html; https://www.huize.com/product/detail-104305.html; https://zhuanlan.zhihu.com/p/707257369</t>
         </is>
       </c>
     </row>
@@ -3677,7 +3802,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>在售（依据为2026年沃保等仍在更新其购买指南与价格文章，未见下架公告；非一线经纪平台主推，建议下单前在投保页复核）</t>
+          <t>已停售（2026-09-13复核改判：奶爸保产品库与沃保2026-02-11文章两个独立来源均指向停售；未见官方下架公告，停售确切时间未披露）</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -3768,7 +3893,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>https://news.vobao.com/article/1119541103197630322.shtml; https://www.vobao.com/top/1121180423502442410.shtml</t>
+          <t>https://news.vobao.com/article/1119541103197630322.shtml; https://www.vobao.com/top/1121180423502442410.shtml; https://www.naibabao.com/chanpin/list-4/p3.html; https://news.vobao.com/article/1163425768636208860.shtml</t>
         </is>
       </c>
     </row>
@@ -4003,7 +4128,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>https://www.xiaoyusan.com/insurance/detail?chn=search2022&amp;id=179280; https://zhuanlan.zhihu.com/p/2055345776465908379; https://www.shenlanbao.com/wenda/3-717806; https://www.huize.com/product/detail-104180.html</t>
+          <t>https://www.xiaoyusan.com/insurance/detail?chn=search2022&amp;id=179280; https://zhuanlan.zhihu.com/p/2055345776465908379; https://www.shenlanbao.com/wenda/3-717806; https://www.huize.com/product/detail-104180.html; https://m.huize.com/study/detail-577153.html</t>
         </is>
       </c>
     </row>
@@ -4238,6 +4363,124 @@
       <c r="W8" s="2" t="inlineStr">
         <is>
           <t>https://www.zhongan.com/productlist/36-41; https://www.zhongan.com/channel/public/cpjbxx2021_ywx.html; https://m.zhongan.com/gp/99420625?cid=210000170003&amp;templateType=B; https://ihealth.zhongan.com/insure/gt?goodsCode=G202204080050; https://health.zacdn.cn/static/insurance/apply/h5/feepremium/premiumRate_CX48CX46CX44_G202204080050.pdf; https://cdn-health.zhongan.com/hic/library/resource/insurance_document/G202204260001/%E8%B4%B9%E7%8E%87%E8%A1%A8.pdf; https://static.zhongan.com/upload/online/material/1752808764250.pdf; https://static.zhongan.com/upload/online/material/1752808719698.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>ACC-08</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>小蜜蜂（无畏版）1-6类意外险 · 计划四（50万档）</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>众安在线财产保险股份有限公司（众安保险）</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>互联网（深蓝保经纪推荐+立即投保入口，投保页经慧择CPS通道cps.qixin18.com承载数据，销售方为深圳市得同保险代理有限公司；众安官网直销产品列表未见此产品，名为小蜜蜂但承保方为众安而非太保，以备案条款为准）</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>18-60周岁（投保人须年满18周岁有完全民事行为能力；每一被保险人同一保险期间限投1份；1-6类职业可投、暂不接受7类及以上，职业分类以众安职业分类表为准；出险时实际职业超过承保类别的事故为除外责任；特种作业须持特种作业操作证/特种设备作业证，无证不赔；投保时已有意外险累计意外身故保额（不含航空）超100万者不可投）</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1年，一次交清（投保页另示支持分期支付，以投保页为准）；不保证续保，期满需重新投保并经保险公司同意；保单生效日最早为投保并成功缴纳保费的第5日零时（约T+5；深蓝保测评页口径为投保后第6天）</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>意外伤害无等待期；投保页与测评摘要均未见等待期约定（猝死责任亦未见等待期表述，以条款为准）</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>无犹豫期约定：投保须知载明保单生效前可全额退保；生效后退保按未满期保费退费，未满期保险费=保险费×[1-（保险合同已经过天数/保险期间天数）]，经过天数不足一天按一天计</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>成人综合意外（1-6类职业/中高危职业可投）</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>计划一：意外身故/伤残10万，意外医疗1.5万（免赔100元社保内90%），猝死2万，住院津贴50元/天，交通意外额外最高30万；148元/年（1-4类职业）、318元/年（5-6类职业）
+计划二：意外身故/伤残20万，意外医疗2.5万，猝死5万，住院津贴50元/天，交通意外额外最高30万；298元/年（1-4类职业）、628元/年（5-6类职业）
+计划三：意外身故/伤残30万，意外医疗3.5万，猝死6万，住院津贴100元/天，交通意外额外最高30万；450元/年（1-4类职业）、928元/年（5-6类职业）
+计划四：意外身故/伤残50万，意外医疗5万，猝死8万，住院津贴100元/天，交通意外额外最高50万；625元/年（1-4类职业）、1248元/年（5-6类职业）</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>计划四意外身故50万（计划一10万/计划二20万/计划三30万）；另有交通意外身故/伤残额外赔，计划一至三最高30万、计划四最高50万（营运交通工具乘客意外伤害保险条款互联网2023版A款）</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>意外伤残按伤残等级10%-100%比例赔付，伤残保额与身故保额一致（计划四50万）</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>意外医疗计划四5万（计划一1.5万/计划二2.5万/计划三3.5万）；仅限符合当地社会基本医疗保险规定的必需合理费用（社保内），每次事故绝对免赔额100元，扣除免赔后按90%赔付（经/未经社保报销均90%）；费用补偿型（可从其他保险计划获得补偿的部分需扣除）；限二级及以上公立医院，除外医院名单较长（涉及北京平谷/密云/怀柔、河南新乡/焦作/濮阳/开封等多地、四川宜宾/泸州、山东烟台栖霞/莱州等，详见投保须知第7条）</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>意外住院津贴：计划一/二50元/天、计划三/四100元/天；每次事故免赔3天；单次赔付计划一/二以30天为限、计划三/四以60天为限（投保须知统一口径为每次事故以60天为限）；累计以180天为限</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>交通意外身故/伤残额外赔（营运交通工具）：计划一至三最高30万、计划四最高50万；无航空意外高额额外赔责任</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>猝死保险金：计划一2万/计划二5万/计划三6万/计划四8万；定义为平素身体健康或表面健康的人因潜在疾病、机能障碍在出现症状后24小时内发生的突然死亡</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="n">
+        <v>625</v>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>18-60周岁统一年龄费率，按职业类别两档计价（官方费率表，元/年）；annual_premium取产品名对应档位计划四（50万档）1-4类职业价格</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>亮点：1-6类职业可投（货车司机、高空作业等中高危职业友好），无健康告知（深蓝保口径）；扩展承保坠落高度基准面10米及以下的高空坠落意外（普通意外险通常2米以上即免责）；众安承保，风险评级A类、综合偿付能力充足率241.21%。短板：意外医疗仅报社保内费用且每次免赔100元、按90%赔付，明显弱于大护甲9号/小蜜蜂6号的不限社保0免赔100%；身故/伤残保额上限仅50万；保费按职业类别分档，5-6类价格约为1-4类的两倍；特定医院免责、特种行业无证不赔、职业变更后超类别出险不赔；深蓝保点评：低风险职业人群建议改选性价比更高的1-3类职业产品（如大护甲9号/小蜜蜂6号）</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.shenlanbao.com/pingce/1232641840678633472; https://cps.qixin18.com/apps/cps/gw1070454/product/detail?prodId=104778&amp;planId=129923; https://files2.huizecdn.com/file2/M00/86/F2/rBYA3GYePJGAbV-OAAEtJYt8YdM919.pdf; https://news.vobao.com/article/1163425768636208860.shtml</t>
         </is>
       </c>
     </row>
@@ -4252,7 +4495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4291,7 +4534,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -4303,7 +4546,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 18:40</t>
+          <t>2026-09-13 16:42</t>
         </is>
       </c>
     </row>
@@ -4315,7 +4558,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -4327,7 +4570,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>11/10/7 款</t>
+          <t>12/10/8 款</t>
         </is>
       </c>
     </row>
@@ -4386,10 +4629,22 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>Agent用Markdown</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>md/insurance_products.md (单文件,适合直接喂给LLM/Agent)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
           <t>免责声明</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>本表仅供研究参考,不构成投保建议;保险产品更新换代频繁,以保险公司官方披露的条款与费率为准</t>
         </is>
